--- a/yellow-server/data/results/实口地址高风险统计.xlsx
+++ b/yellow-server/data/results/实口地址高风险统计.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,13 +412,31 @@
       <c r="D1" t="str">
         <v>实口所属派出所</v>
       </c>
+      <c r="E1" t="str">
+        <v>异常资金</v>
+      </c>
+      <c r="F1" t="str">
+        <v>入住次数</v>
+      </c>
+      <c r="G1" t="str">
+        <v>同住男人数</v>
+      </c>
+      <c r="H1" t="str">
+        <v>前科次数</v>
+      </c>
+      <c r="I1" t="str">
+        <v>前科人员</v>
+      </c>
+      <c r="J1" t="str">
+        <v>前科情况</v>
+      </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>新桥镇新中街10000号</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="str" xml:space="preserve">
         <v xml:space="preserve">姓名：张三——证件号码：310227199002301001——原始地址：新桥镇新中街10000号10001室——实口所属派出所：新桥派出所
@@ -430,16 +448,33 @@
 姓名：小胡——证件号码：310227199002301007——原始地址：新桥镇新中街10000号10007室——实口所属派出所：新桥派出所
 姓名：小刚——证件号码：310227199002301008——原始地址：新桥镇新中街10000号10008室——实口所属派出所：新桥派出所
 姓名：小金——证件号码：310227199002301009——原始地址：新桥镇新中街10000号10009室——实口所属派出所：新桥派出所
-姓名：小钱——证件号码：310227199002301000——原始地址：新桥镇新中街10000号100010室——实口所属派出所：新桥派出所
 姓名：小钱——证件号码：310227199002301010——原始地址：新桥镇新中街10000号100010室——实口所属派出所：新桥派出所</v>
       </c>
       <c r="D2" t="str">
         <v>新桥派出所</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/yellow-server/data/results/实口地址高风险统计.xlsx
+++ b/yellow-server/data/results/实口地址高风险统计.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -411,24 +411,6 @@
       </c>
       <c r="D1" t="str">
         <v>实口所属派出所</v>
-      </c>
-      <c r="E1" t="str">
-        <v>异常资金</v>
-      </c>
-      <c r="F1" t="str">
-        <v>入住次数</v>
-      </c>
-      <c r="G1" t="str">
-        <v>同住男人数</v>
-      </c>
-      <c r="H1" t="str">
-        <v>前科次数</v>
-      </c>
-      <c r="I1" t="str">
-        <v>前科人员</v>
-      </c>
-      <c r="J1" t="str">
-        <v>前科情况</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -453,28 +435,10 @@
       <c r="D2" t="str">
         <v>新桥派出所</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>